--- a/docs/xlsform-template/dcp-xlsform-template.xlsx
+++ b/docs/xlsform-template/dcp-xlsform-template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -435,8 +435,8 @@
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="46" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
@@ -1025,200 +1025,6 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>begin repeat</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>members</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Household members</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>گھر کے افراد</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>${hh_size}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>member_name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Member's name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>فرد کا نام</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>member_age</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>عمر</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>${member_age} &gt;= 0 and ${member_age} &lt; 120</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Age must be between 0 and 119.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one relation</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>member_relation</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Relation to head</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>سربراہ سے رشتہ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one yes_no</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>member_in_school</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Attends school?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>کیا اسکول جاتا ہے؟</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Relevance inside a repeat is evaluated per instance.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>${member_age} &gt;= 5 and ${member_age} &lt;= 18</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>end repeat</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1231,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1391,94 +1197,6 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>گنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>head</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Head</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>سربراہ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>spouse</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Spouse</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>شریک حیات</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>child</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Child</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>بچہ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Other relative</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>دیگر رشتہ دار</t>
         </is>
       </c>
     </row>

--- a/docs/xlsform-template/dcp-xlsform-template.xlsx
+++ b/docs/xlsform-template/dcp-xlsform-template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,21 +27,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDE5F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,11 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,76 +415,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="37" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>label::Urdu (ur)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label::Sindhi (sd)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>hint::English (en)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>appearance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>calculation</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>repeat_count</t>
         </is>
       </c>
     </row>
@@ -520,13 +506,19 @@
           <t>گھرانہ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>گهراڻو</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,13 +541,19 @@
           <t>یہ فارم ہر وہ سوال دکھاتا ہے جو DCP جمع کر سکتا ہے۔</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>هي فارم هر اهو سوال ڏيکاري ٿو جيڪو DCP گڏ ڪري سگهي ٿو.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -580,27 +578,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>گهر جي سربراهه جو نالو</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Free text.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>string-length(${head_name}) &lt;= 60</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Please keep the name under 60 characters.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,27 +629,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Whole number. Drives the roster below.</t>
+          <t>هتي ڪيترا ماڻهو رهن ٿا؟</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Whole number. Drives the roster in the other workbook.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>${hh_size} &gt; 0 and ${hh_size} &lt;= 30</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>A household must have between 1 and 30 members.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -670,23 +680,29 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>مهيني جي آمدني</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Decimals allowed.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>${monthly_income} &gt;= 0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Income cannot be negative.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -709,25 +725,31 @@
           <t>انٹرویو کی تاریخ</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>انٽرويو جي تاريخ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>${interview_date} &lt;= today()</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>The interview cannot be in the future.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -752,19 +774,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>ڇا هي گهراڻو زمين جو مالڪ آهي؟</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Single selection from the choices sheet.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -789,31 +817,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Only asked when the answer above is yes — this is relevance, not a skip.</t>
+          <t>ڪيترا ايڪڙ؟</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Only asked when the answer above is yes — relevance, not a skip.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>${owns_land} = 'yes'</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>${land_acres} &gt; 0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Enter an area greater than zero.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -838,27 +872,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>ڪهڙا فصل پوکيا وڃن ٿا؟</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Multiple selection.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>${owns_land} = 'yes'</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>count-selected(${crops_grown}) &lt;= 4</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Choose at most four crops.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -883,19 +923,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>ضلعو</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>An external list. The CSV ships beside this workbook.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -918,13 +964,19 @@
           <t>مکان کی تصویر</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>گهر جي تصوير</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -947,13 +999,19 @@
           <t>مکان کا مقام</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>گهر جو هنڌ</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -976,13 +1034,19 @@
           <t>جواب دہندہ کے دستخط</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>جواب ڏيندڙ جا صحيح</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1002,12 +1066,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>${monthly_income} div ${hh_size}</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1025,6 +1091,191 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>screening</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Screening — these three share one screen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ابتدائی سوالات</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ابتدائي سوال</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_one yes_no</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Does the respondent consent?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>کیا جواب دہندہ رضامند ہے؟</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ڇا جواب ڏيندڙ راضي آهي؟</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>visit_number</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Visit number</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>دورے کا نمبر</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>دوري جو نمبر</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A literal `default`, typed to match the question.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>listed_head_name</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Head of household (prefilled)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>گھر کا سربراہ</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>گهر جو سربراهه</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>A `default` that reads an earlier answer — this is what your Person Id questions become.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>${head_name}</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1037,34 +1288,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>list_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>label::English (en)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>label::Urdu (ur)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label::Sindhi (sd)</t>
         </is>
       </c>
     </row>
@@ -1089,6 +1339,11 @@
           <t>ہاں</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ها</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1111,6 +1366,11 @@
           <t>نہیں</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>نه</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1133,6 +1393,11 @@
           <t>گندم</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ڪڻڪ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1155,6 +1420,11 @@
           <t>چاول</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>چانور</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1177,6 +1447,11 @@
           <t>کپاس</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ڪپهه</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1197,6 +1472,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>گنا</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ڪمند</t>
         </is>
       </c>
     </row>
@@ -1213,30 +1493,24 @@
   </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>form_title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>form_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>default_language</t>
         </is>
